--- a/tenders.xlsx
+++ b/tenders.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מכרזים חקלאיים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="מכרזים חקלאיים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,26 @@
       <color rgb="00FFFFFF"/>
       <sz val="15"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001155CC"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,8 +61,18 @@
         <fgColor rgb="002E8B57"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9971C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,14 +80,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -443,14 +500,116 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🌾  מכרזים חקלאיים · משק אנג׳ל · אזור עמק יזרעאל</t>
+          <t>🌾  מכרזים חקלאיים · אנגל · אזור עמק יזרעאל</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>📅  פברואר 2026   (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>מכרז</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>סוג המכרז</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>מיקום</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>שטח (מ״ר)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>תאריך פרסום</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>מועד אחרון להגשה</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>מפרסם</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>פרטי קשר</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>קישור</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>גידולי שדה בעל</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>כוונה להתקשרות</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>נצרת</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>4024</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>רשות מקרקעי ישראל</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>נתנאל ירדן · לא צוין טלפון · netanely@land.gov.il</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>פתיחה ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tenders.xlsx
+++ b/tenders.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -601,14 +601,214 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>📅  אוקטובר 2023   (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>מכרז</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>סוג המכרז</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>מיקום</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>שטח (מ״ר)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>תאריך פרסום</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>מועד אחרון להגשה</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>מפרסם</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>פרטי קשר</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>קישור</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>שאוכת נג'ארה גד"ש</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>פטור</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>דברת ב</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>5950</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>23/10/2023</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>רשות מקרקעי ישראל</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>שירן אלבז · לא צוין טלפון</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>פתיחה ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>📅  מרץ 2023   (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>מכרז</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>סוג המכרז</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>מיקום</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>שטח (מ״ר)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>תאריך פרסום</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>מועד אחרון להגשה</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>מפרסם</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>פרטי קשר</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>קישור</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>אבראהים חאלדי גד"ש</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>פטור</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>מ.א. יזרעאל ב</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>10520</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>03/03/2023</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>רשות מקרקעי ישראל</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>שירן אלבז · לא צוין טלפון</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>פתיחה ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tenders.xlsx
+++ b/tenders.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,26 +30,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="15"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="001155CC"/>
-      <sz val="11"/>
-      <u val="single"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -61,18 +43,8 @@
         <fgColor rgb="002E8B57"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9971C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -80,43 +52,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00DDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -504,312 +447,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>📅  פברואר 2026   (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>מכרז</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>סוג המכרז</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>מיקום</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>שטח (מ״ר)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>תאריך פרסום</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>מועד אחרון להגשה</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>מפרסם</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>פרטי קשר</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>קישור</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>גידולי שדה בעל</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>כוונה להתקשרות</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>נצרת</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>4024</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>16/02/2026</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>רשות מקרקעי ישראל</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>נתנאל ירדן · לא צוין טלפון · netanely@land.gov.il</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>פתיחה ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>📅  אוקטובר 2023   (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>מכרז</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>סוג המכרז</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>מיקום</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>שטח (מ״ר)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>תאריך פרסום</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>מועד אחרון להגשה</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>מפרסם</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>פרטי קשר</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>קישור</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>שאוכת נג'ארה גד"ש</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>פטור</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>דברת ב</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>5950</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>23/10/2023</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>רשות מקרקעי ישראל</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>שירן אלבז · לא צוין טלפון</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>פתיחה ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>📅  מרץ 2023   (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>מכרז</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>סוג המכרז</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>מיקום</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>שטח (מ״ר)</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>תאריך פרסום</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>מועד אחרון להגשה</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>מפרסם</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>פרטי קשר</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>קישור</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>אבראהים חאלדי גד"ש</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>פטור</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>מ.א. יזרעאל ב</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>10520</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>03/03/2023</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>רשות מקרקעי ישראל</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>שירן אלבז · לא צוין טלפון</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>פתיחה ↗</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A11:I11"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId6"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tenders.xlsx
+++ b/tenders.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,26 @@
       <color rgb="00FFFFFF"/>
       <sz val="15"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001155CC"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,8 +61,18 @@
         <fgColor rgb="002E8B57"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9971C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,14 +80,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -447,10 +504,112 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>📅  פברואר 2026   (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>מכרז</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>סוג המכרז</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>מיקום</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>שטח (מ״ר)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>תאריך פרסום</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>מועד אחרון להגשה</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>מפרסם</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>פרטי קשר</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>קישור</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>גידולי שדה בעל</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>כוונה להתקשרות</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>נצרת</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>4024</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>רשות מקרקעי ישראל</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>נתנאל ירדן · לא צוין טלפון · netanely@land.gov.il</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>פתיחה ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tenders.xlsx
+++ b/tenders.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,11 @@
       <color rgb="001155CC"/>
       <sz val="11"/>
       <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B23B2E"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -98,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -113,6 +118,9 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -483,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -507,7 +515,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>📅  פברואר 2026   (1)</t>
+          <t>📅  יולי 2026   (1)</t>
         </is>
       </c>
     </row>
@@ -561,54 +569,150 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>הליך הסדרת רישיון לא בלעדי למסחור שתילי זית מזן "אסקל"</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>כוונה להתקשרות</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>02/08/2026 ,00:00 להגשת השגה פניה למפרסם</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>משרד החקלאות וביטחון המזון - מינהל המחקר החקלאי, מכון וולקני</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>ימית ממן · לא צוין טלפון · tendercommittee@volcani.agri.gov.il</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>פתיחה ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>📅  פברואר 2026   (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>מכרז</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>סוג המכרז</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>מיקום</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>שטח (מ״ר)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>תאריך פרסום</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>מועד אחרון להגשה</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>מפרסם</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>פרטי קשר</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>קישור</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>גידולי שדה בעל</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>כוונה להתקשרות</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>נצרת</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>4024</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>16/02/2026</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>רשות מקרקעי ישראל</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>נתנאל ירדן · לא צוין טלפון · netanely@land.gov.il</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>פתיחה ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tenders.xlsx
+++ b/tenders.xlsx
@@ -54,7 +54,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F7F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -124,6 +129,18 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
@@ -491,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -515,7 +532,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>📅  יולי 2026   (1)</t>
+          <t>📅  יולי 2026   (3)</t>
         </is>
       </c>
     </row>
@@ -569,7 +586,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>הליך הסדרת רישיון לא בלעדי למסחור שתילי זית מזן "אסקל"</t>
+          <t>התקשרות בפטור ממכרז לפי תקנה 3 (29) ספק יחיד לקבלת שירותים לפעילות שוטפת של המעבדה לבריאות הדגים בניר דוד של א</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -581,122 +598,200 @@
       <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>09/08/2026 ,05:30 להגשת השגה פניה למפרסם</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>משרד החקלאות ובטחון המזון</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>משה חליווה · לא צוין טלפון · mosheh@moag.gov.il</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>פתיחה ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>התקשרות בפטור ממכרז לפי תקנה 3 (29) ספק יחיד לקבלת שירותים לפעילות שוטפת של המעבדה לבריאות הדגים בניר דוד של א</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>כוונה להתקשרות</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>09/08/2026 ,05:30 להגשת השגה פניה למפרסם</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>משרד החקלאות ובטחון המזון</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>משה חליווה · לא צוין טלפון · mosheh@moag.gov.il</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>פתיחה ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>הליך הסדרת רישיון לא בלעדי למסחור שתילי זית מזן "אסקל"</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>כוונה להתקשרות</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>02/08/2026 ,00:00 להגשת השגה פניה למפרסם</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>משרד החקלאות וביטחון המזון - מינהל המחקר החקלאי, מכון וולקני</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>ימית ממן · לא צוין טלפון · tendercommittee@volcani.agri.gov.il</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>פתיחה ↗</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>📅  פברואר 2026   (1)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>מכרז</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>סוג המכרז</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>מיקום</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>שטח (מ״ר)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>תאריך פרסום</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>מועד אחרון להגשה</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>מפרסם</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>פרטי קשר</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>קישור</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>גידולי שדה בעל</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>כוונה להתקשרות</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>נצרת</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>4024</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>16/02/2026</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>רשות מקרקעי ישראל</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>נתנאל ירדן · לא צוין טלפון · netanely@land.gov.il</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>פתיחה ↗</t>
         </is>
@@ -705,14 +800,18 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tenders.xlsx
+++ b/tenders.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>📅  יולי 2026   (3)</t>
+          <t>📅  יולי 2026   (2)</t>
         </is>
       </c>
     </row>
@@ -661,137 +661,98 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>הליך הסדרת רישיון לא בלעדי למסחור שתילי זית מזן "אסקל"</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>כוונה להתקשרות</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>14/07/2026</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>02/08/2026 ,00:00 להגשת השגה פניה למפרסם</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>משרד החקלאות וביטחון המזון - מינהל המחקר החקלאי, מכון וולקני</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>ימית ממן · לא צוין טלפון · tendercommittee@volcani.agri.gov.il</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>פתיחה ↗</t>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>📅  פברואר 2026   (1)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>📅  פברואר 2026   (1)</t>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>מכרז</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>סוג המכרז</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>מיקום</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>שטח (מ״ר)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>תאריך פרסום</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>מועד אחרון להגשה</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>מפרסם</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>פרטי קשר</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>קישור</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>מכרז</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>סוג המכרז</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>מיקום</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>שטח (מ״ר)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>תאריך פרסום</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>מועד אחרון להגשה</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>מפרסם</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>פרטי קשר</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>קישור</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>גידולי שדה בעל</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>כוונה להתקשרות</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>נצרת</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>4024</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>16/02/2026</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>רשות מקרקעי ישראל</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>נתנאל ירדן · לא צוין טלפון · netanely@land.gov.il</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>פתיחה ↗</t>
         </is>
@@ -800,7 +761,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A8:I8"/>
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <hyperlinks>
@@ -808,10 +769,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
